--- a/Catch models/quantis_msy_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_msy_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1385.87525488885</v>
+        <v>1021.67083426327</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1761.349824529608</v>
+        <v>1257.79326447176</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1966.87998897556</v>
+        <v>1391.3986822337</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2205.074376103765</v>
+        <v>1531.51643351724</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2895.225202631301</v>
+        <v>2042.627792777517</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_msy_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1021.67083426327</v>
+        <v>1267.21652484056</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1257.79326447176</v>
+        <v>1601.10668568905</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1391.3986822337</v>
+        <v>1783.57073574328</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1531.51643351724</v>
+        <v>1958.14253003991</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2042.627792777517</v>
+        <v>2429.25671400464</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_msy_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1267.21652484056</v>
+        <v>1341.387917241068</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1601.10668568905</v>
+        <v>1665.469556530295</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1783.57073574328</v>
+        <v>1834.37868295726</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1958.14253003991</v>
+        <v>1987.47293633985</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2429.25671400464</v>
+        <v>2427.479456772283</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_msy_conjunto_cmsy.xlsx
+++ b/Catch models/quantis_msy_conjunto_cmsy.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1341.387917241068</v>
+        <v>1315.59251794557</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>1665.469556530295</v>
+        <v>1657.049114065657</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>1834.37868295726</v>
+        <v>1830.60740005623</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1987.47293633985</v>
+        <v>1983.859136938217</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2427.479456772283</v>
+        <v>2420.560220641916</v>
       </c>
     </row>
   </sheetData>
